--- a/Dashboards/Data final/empleo_scorecard.xlsx
+++ b/Dashboards/Data final/empleo_scorecard.xlsx
@@ -381,7 +381,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>32.87280611429926</v>
+        <v>33.02956536674139</v>
       </c>
     </row>
     <row r="3">
@@ -394,7 +394,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>66.2190238964765</v>
+        <v>66.05793388966839</v>
       </c>
     </row>
     <row r="4">
